--- a/templates/sales-quote.xlsx
+++ b/templates/sales-quote.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="11214"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DHKIM\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jangjingang/dev/smerp_next/templates/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{009B0505-C8D2-47FE-AD87-557F41576AC6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C8E100C-D7F2-2548-AA1B-C49109574973}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38280" yWindow="2490" windowWidth="29040" windowHeight="15720" tabRatio="580" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="38400" windowHeight="21100" tabRatio="580" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="견적서" sheetId="14" r:id="rId1"/>
@@ -18,7 +18,20 @@
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">견적서!$B$1:$G$43</definedName>
   </definedNames>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -70,7 +83,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="32">
   <si>
     <r>
       <rPr>
@@ -1365,1348 +1378,55 @@
     </r>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
-  <si>
-    <t>김대훈(070-8892-1455)</t>
-    <phoneticPr fontId="81" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve"> -19</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>인치표준랙</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> (ANSI/EIA-310-D </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>규격</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>)
- -(H)2,000*(W)600*(D)1,070 mm / 42U /Black
- -</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>케이지너트</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>타입</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>마운트프레임</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">( </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>유닛넘버링</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>)
- -</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>재질</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">: SPCC </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve">냉간압연강판
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> -</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>두께</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> : 1.2T, 1.5T, 2.0T
- -</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>전면도어</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> : </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>벌집타공도어</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> &amp; </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>스윙핸들</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve">잠금장치
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> -</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>후면도어</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> : </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>양문형</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>벌집타공도어</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> &amp; </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>스윙핸들</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve">잠금장치
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> -</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>사이드판넬</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> : </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>스틸판넬</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> * 4</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>개</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">  ( </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>별도포장납품</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> )
- -</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>하중선반</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> :  </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>선반</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> 2</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve">개
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> -</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>전원</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> : -</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>[견적서 나간 회사] 귀중</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>[견적 받는 담당자]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>[담당자 이메일]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>[별도협의 or 입고일이 정해진 날짜]</t>
-    <phoneticPr fontId="81" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>견적서</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>나간</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>날짜</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>예시</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>_</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>견적일로부터</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> 7</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>일이내</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>[</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>시장</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>상황에</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>따라</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>다름</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>]</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>예시_계산서 발행 후 익월 말 현금 조건[기거래규정 or 별도협의, 첫 거래일 경우 발주 및 납품 전 일시불 조건]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>예시</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>_02-1234-5678</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>예시</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>_070-1234-5678</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>예시</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>_010-1234-5678</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>예시_BYC 통합서버 관리 건</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>AL 10</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>구</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve"> 16A MCCB </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve">랙전원
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>&gt;</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>단상</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>3</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>선식</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve">, 220V, 30A </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>배선용차단기</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve">(MCCB), </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve">단자대
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>&gt;3C*4.0SQ*2.5M
-&gt;</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>출력소켓</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve"> : KS </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>타입소켓</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve"> * 10</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve">개
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>&gt;</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>입력플러그</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve"> : 220V 16A IP67 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>플러그</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>(TYP 290)
-&gt;</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>인입선용</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>소켓</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve"> : 220V 16A IP67 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>소켓</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve">(TYP 552) </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>제공</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>BYC, 1</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>층</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>인도조건</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>배송기사</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> 1</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>인</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>하차</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>시</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>도움필요</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>[견적서의 상세 내역 or 견적서 추가 내용]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>[</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>제품명</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>]</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>[품목명]
-예시_서버랙</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>[품목명]
-예시_전원</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>[품목명]
-예시_운송비</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="42">
-    <numFmt numFmtId="8" formatCode="&quot;₩&quot;#,##0.00;[Red]\-&quot;₩&quot;#,##0.00"/>
-    <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
-    <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="176" formatCode="#,##0_ "/>
-    <numFmt numFmtId="177" formatCode="#,##0.0000"/>
-    <numFmt numFmtId="178" formatCode="#"/>
-    <numFmt numFmtId="179" formatCode="0.0%"/>
-    <numFmt numFmtId="180" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="181" formatCode="_(* #,##0.0_);_(* \(#,##0.0\);_(* &quot;-&quot;?_);_(@_)"/>
-    <numFmt numFmtId="182" formatCode="0.00;[Red]0.00"/>
-    <numFmt numFmtId="183" formatCode="0.0;[Red]0.0"/>
-    <numFmt numFmtId="184" formatCode="_(* #,##0.00000_);_(* \(#,##0.00000\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="185" formatCode="_(&quot;$&quot;* #,##0.0_);_(&quot;$&quot;* \(#,##0.0\);_(&quot;$&quot;* &quot;-&quot;_);_(@_)"/>
-    <numFmt numFmtId="186" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="187" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="188" formatCode="####"/>
-    <numFmt numFmtId="189" formatCode="\,##"/>
-    <numFmt numFmtId="190" formatCode="#.00"/>
-    <numFmt numFmtId="191" formatCode="##"/>
-    <numFmt numFmtId="192" formatCode="###,###,"/>
-    <numFmt numFmtId="193" formatCode="0.00&quot;  &quot;"/>
-    <numFmt numFmtId="194" formatCode="0.000&quot;  &quot;"/>
-    <numFmt numFmtId="195" formatCode="_-* #,##0\ _F_-;\-* #,##0\ _F_-;_-* &quot;-&quot;\ _F_-;_-@_-"/>
-    <numFmt numFmtId="196" formatCode="_-* #,##0.00\ _F_-;\-* #,##0.00\ _F_-;_-* &quot;-&quot;??\ _F_-;_-@_-"/>
-    <numFmt numFmtId="197" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;_);_(@_)"/>
-    <numFmt numFmtId="198" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="199" formatCode="_-* #,##0\ &quot;F&quot;_-;\-* #,##0\ &quot;F&quot;_-;_-* &quot;-&quot;\ &quot;F&quot;_-;_-@_-"/>
-    <numFmt numFmtId="200" formatCode="_-* #,##0.00\ &quot;F&quot;_-;\-* #,##0.00\ &quot;F&quot;_-;_-* &quot;-&quot;??\ &quot;F&quot;_-;_-@_-"/>
-    <numFmt numFmtId="201" formatCode="_-* #,##0.00_-;&quot;₩&quot;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="202" formatCode="#,###.0,,\ \ ;\(#,###.0,,\)\ \ "/>
-    <numFmt numFmtId="203" formatCode="###"/>
-    <numFmt numFmtId="204" formatCode="_-* #,##0.0_-;\-* #,##0.0_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="205" formatCode="_ &quot;₩&quot;* #,##0.0000000_ ;_ &quot;₩&quot;* &quot;₩&quot;\-#,##0.0000000_ ;_ &quot;₩&quot;* &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="206" formatCode="&quot;$&quot;#,##0_);\(&quot;$&quot;#,##0\)"/>
-    <numFmt numFmtId="207" formatCode="#,##0,_);[Red]\(#,##0,\);&quot;-  &quot;"/>
-    <numFmt numFmtId="208" formatCode="#,##0.0,_);[Red]\(#,##0.0,\);&quot;-  &quot;"/>
-    <numFmt numFmtId="209" formatCode="#,###,\ \ ;\(#,###,\)\ \ "/>
-    <numFmt numFmtId="210" formatCode="_ * #,##0.000000_ ;_ * &quot;₩&quot;\-#,##0.000000_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="211" formatCode="#,##0.0"/>
-    <numFmt numFmtId="212" formatCode="yyyy&quot;년&quot;\ m&quot;월&quot;\ d&quot;일&quot;;@"/>
-    <numFmt numFmtId="213" formatCode="mm&quot;월&quot;\ dd&quot;일&quot;"/>
-    <numFmt numFmtId="214" formatCode="#,##0_);[Red]\(#,##0\)"/>
+  <numFmts count="41">
+    <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="176" formatCode="&quot;₩&quot;#,##0.00;[Red]\-&quot;₩&quot;#,##0.00"/>
+    <numFmt numFmtId="177" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="179" formatCode="#,##0_ "/>
+    <numFmt numFmtId="180" formatCode="#,##0.0000"/>
+    <numFmt numFmtId="181" formatCode="#"/>
+    <numFmt numFmtId="182" formatCode="0.0%"/>
+    <numFmt numFmtId="183" formatCode="_(* #,##0.0_);_(* \(#,##0.0\);_(* &quot;-&quot;?_);_(@_)"/>
+    <numFmt numFmtId="184" formatCode="0.00;[Red]0.00"/>
+    <numFmt numFmtId="185" formatCode="0.0;[Red]0.0"/>
+    <numFmt numFmtId="186" formatCode="_(* #,##0.00000_);_(* \(#,##0.00000\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="187" formatCode="_(&quot;$&quot;* #,##0.0_);_(&quot;$&quot;* \(#,##0.0\);_(&quot;$&quot;* &quot;-&quot;_);_(@_)"/>
+    <numFmt numFmtId="188" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="189" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="190" formatCode="####"/>
+    <numFmt numFmtId="191" formatCode="\,##"/>
+    <numFmt numFmtId="192" formatCode="#.00"/>
+    <numFmt numFmtId="193" formatCode="##"/>
+    <numFmt numFmtId="194" formatCode="###,###,"/>
+    <numFmt numFmtId="195" formatCode="0.00&quot;  &quot;"/>
+    <numFmt numFmtId="196" formatCode="0.000&quot;  &quot;"/>
+    <numFmt numFmtId="197" formatCode="_-* #,##0\ _F_-;\-* #,##0\ _F_-;_-* &quot;-&quot;\ _F_-;_-@_-"/>
+    <numFmt numFmtId="198" formatCode="_-* #,##0.00\ _F_-;\-* #,##0.00\ _F_-;_-* &quot;-&quot;??\ _F_-;_-@_-"/>
+    <numFmt numFmtId="199" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;_);_(@_)"/>
+    <numFmt numFmtId="200" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="201" formatCode="_-* #,##0\ &quot;F&quot;_-;\-* #,##0\ &quot;F&quot;_-;_-* &quot;-&quot;\ &quot;F&quot;_-;_-@_-"/>
+    <numFmt numFmtId="202" formatCode="_-* #,##0.00\ &quot;F&quot;_-;\-* #,##0.00\ &quot;F&quot;_-;_-* &quot;-&quot;??\ &quot;F&quot;_-;_-@_-"/>
+    <numFmt numFmtId="203" formatCode="_-* #,##0.00_-;&quot;₩&quot;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="204" formatCode="#,###.0,,\ \ ;\(#,###.0,,\)\ \ "/>
+    <numFmt numFmtId="205" formatCode="###"/>
+    <numFmt numFmtId="206" formatCode="_-* #,##0.0_-;\-* #,##0.0_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="207" formatCode="_ &quot;₩&quot;* #,##0.0000000_ ;_ &quot;₩&quot;* &quot;₩&quot;\-#,##0.0000000_ ;_ &quot;₩&quot;* &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="208" formatCode="&quot;$&quot;#,##0_);\(&quot;$&quot;#,##0\)"/>
+    <numFmt numFmtId="209" formatCode="#,##0,_);[Red]\(#,##0,\);&quot;-  &quot;"/>
+    <numFmt numFmtId="210" formatCode="#,##0.0,_);[Red]\(#,##0.0,\);&quot;-  &quot;"/>
+    <numFmt numFmtId="211" formatCode="#,###,\ \ ;\(#,###,\)\ \ "/>
+    <numFmt numFmtId="212" formatCode="_ * #,##0.000000_ ;_ * &quot;₩&quot;\-#,##0.000000_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="213" formatCode="#,##0.0"/>
+    <numFmt numFmtId="214" formatCode="yyyy&quot;년&quot;\ m&quot;월&quot;\ d&quot;일&quot;;@"/>
+    <numFmt numFmtId="215" formatCode="mm&quot;월&quot;\ dd&quot;일&quot;"/>
   </numFmts>
-  <fonts count="93">
+  <fonts count="90">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2775,6 +1495,7 @@
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Geneva"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
@@ -3115,13 +1836,6 @@
       <u/>
       <sz val="10"/>
       <color rgb="FF0000FF"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
@@ -3255,13 +1969,6 @@
       <family val="2"/>
     </font>
     <font>
-      <sz val="8"/>
-      <name val="맑은 고딕"/>
-      <family val="3"/>
-      <charset val="129"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -3297,14 +2004,6 @@
       <u/>
       <sz val="11"/>
       <color rgb="FF000000"/>
-      <name val="돋움"/>
-      <family val="3"/>
-      <charset val="129"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="12"/>
-      <color rgb="FFFF0000"/>
       <name val="돋움"/>
       <family val="3"/>
       <charset val="129"/>
@@ -4536,7 +3235,7 @@
     <xf numFmtId="0" fontId="36" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="13" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="180" fontId="13" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="36" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
@@ -5408,44 +4107,44 @@
     <xf numFmtId="3" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
-    <xf numFmtId="181" fontId="6" fillId="0" borderId="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
-    <xf numFmtId="182" fontId="6" fillId="0" borderId="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
     <xf numFmtId="183" fontId="6" fillId="0" borderId="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
+    <xf numFmtId="184" fontId="6" fillId="0" borderId="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
+    <xf numFmtId="185" fontId="6" fillId="0" borderId="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
-    <xf numFmtId="184" fontId="6" fillId="0" borderId="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
+    <xf numFmtId="186" fontId="6" fillId="0" borderId="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
     <xf numFmtId="3" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0"/>
     <xf numFmtId="4" fontId="22" fillId="0" borderId="0">
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="185" fontId="6" fillId="0" borderId="0"/>
-    <xf numFmtId="185" fontId="6" fillId="0" borderId="0"/>
-    <xf numFmtId="185" fontId="6" fillId="0" borderId="0"/>
-    <xf numFmtId="185" fontId="6" fillId="0" borderId="0"/>
-    <xf numFmtId="185" fontId="6" fillId="0" borderId="0"/>
-    <xf numFmtId="185" fontId="6" fillId="0" borderId="0"/>
-    <xf numFmtId="185" fontId="6" fillId="0" borderId="0"/>
-    <xf numFmtId="185" fontId="6" fillId="0" borderId="0"/>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="186" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="186" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="187" fontId="6" fillId="0" borderId="0"/>
+    <xf numFmtId="187" fontId="6" fillId="0" borderId="0"/>
+    <xf numFmtId="187" fontId="6" fillId="0" borderId="0"/>
+    <xf numFmtId="187" fontId="6" fillId="0" borderId="0"/>
+    <xf numFmtId="187" fontId="6" fillId="0" borderId="0"/>
+    <xf numFmtId="187" fontId="6" fillId="0" borderId="0"/>
+    <xf numFmtId="187" fontId="6" fillId="0" borderId="0"/>
+    <xf numFmtId="187" fontId="6" fillId="0" borderId="0"/>
+    <xf numFmtId="177" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="188" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="188" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="187" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="188" fontId="6" fillId="0" borderId="0">
+    <xf numFmtId="189" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="190" fontId="6" fillId="0" borderId="0">
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="189" fontId="6" fillId="0" borderId="0">
+    <xf numFmtId="191" fontId="6" fillId="0" borderId="0">
       <protection locked="0"/>
     </xf>
     <xf numFmtId="14" fontId="20" fillId="0" borderId="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
@@ -5461,10 +4160,10 @@
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
-    <xf numFmtId="184" fontId="6" fillId="0" borderId="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
+    <xf numFmtId="186" fontId="6" fillId="0" borderId="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
     <xf numFmtId="3" fontId="6" fillId="0" borderId="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="190" fontId="22" fillId="0" borderId="0">
+    <xf numFmtId="192" fontId="22" fillId="0" borderId="0">
       <protection locked="0"/>
     </xf>
     <xf numFmtId="38" fontId="5" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
@@ -5477,10 +4176,10 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="4">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="191" fontId="6" fillId="0" borderId="0">
+    <xf numFmtId="193" fontId="6" fillId="0" borderId="0">
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="191" fontId="6" fillId="0" borderId="0">
+    <xf numFmtId="193" fontId="6" fillId="0" borderId="0">
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -5489,51 +4188,51 @@
     </xf>
     <xf numFmtId="10" fontId="5" fillId="17" borderId="5" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0"/>
-    <xf numFmtId="192" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="194" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="179" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
     <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
     <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
-    <xf numFmtId="184" fontId="6" fillId="0" borderId="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
+    <xf numFmtId="186" fontId="6" fillId="0" borderId="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
     <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
-    <xf numFmtId="193" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="194" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="195" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="196" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="6"/>
     <xf numFmtId="197" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="198" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="6"/>
     <xf numFmtId="199" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="200" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="201" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="201" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="202" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="203" fontId="4" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="30" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="30" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="66" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="66" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
-    <xf numFmtId="202" fontId="9" fillId="0" borderId="7" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0">
+    <xf numFmtId="204" fontId="9" fillId="0" borderId="7" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="28" fillId="0" borderId="0"/>
-    <xf numFmtId="179" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="203" fontId="6" fillId="0" borderId="0">
+    <xf numFmtId="182" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="205" fontId="6" fillId="0" borderId="0">
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="183" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="204" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="185" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="206" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="10" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="205" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="207" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="29" fillId="0" borderId="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
     <xf numFmtId="0" fontId="29" fillId="0" borderId="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
     <xf numFmtId="0" fontId="29" fillId="0" borderId="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
-    <xf numFmtId="184" fontId="6" fillId="0" borderId="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
+    <xf numFmtId="186" fontId="6" fillId="0" borderId="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
     <xf numFmtId="0" fontId="29" fillId="0" borderId="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
-    <xf numFmtId="206" fontId="3" fillId="0" borderId="0">
+    <xf numFmtId="208" fontId="3" fillId="0" borderId="0">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="9" fontId="30" fillId="0" borderId="0" applyFont="0" applyFill="0" applyProtection="0"/>
@@ -5547,20 +4246,20 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="27" fillId="0" borderId="0"/>
     <xf numFmtId="49" fontId="20" fillId="0" borderId="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
-    <xf numFmtId="207" fontId="6" fillId="0" borderId="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
-    <xf numFmtId="208" fontId="6" fillId="0" borderId="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
-    <xf numFmtId="191" fontId="6" fillId="0" borderId="9">
+    <xf numFmtId="209" fontId="6" fillId="0" borderId="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
+    <xf numFmtId="210" fontId="6" fillId="0" borderId="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
+    <xf numFmtId="193" fontId="6" fillId="0" borderId="9">
       <protection locked="0"/>
     </xf>
     <xf numFmtId="37" fontId="33" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyBorder="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="209" fontId="6" fillId="0" borderId="0">
+    <xf numFmtId="211" fontId="6" fillId="0" borderId="0">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="37" fontId="34" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="210" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="211" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="212" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="213" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="37" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
@@ -6281,7 +4980,7 @@
     <xf numFmtId="0" fontId="2" fillId="23" borderId="12" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="14" fillId="0" borderId="0">
+    <xf numFmtId="181" fontId="14" fillId="0" borderId="0">
       <protection locked="0"/>
     </xf>
     <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -6511,319 +5210,319 @@
     <xf numFmtId="0" fontId="43" fillId="25" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="14" fillId="0" borderId="0">
+    <xf numFmtId="181" fontId="14" fillId="0" borderId="0">
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="178" fontId="14" fillId="0" borderId="0">
+    <xf numFmtId="181" fontId="14" fillId="0" borderId="0">
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="41" fontId="66" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="35" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="35" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="41" fontId="35" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="35" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="66" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="35" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="35" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="66" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="66" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="66" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="35" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="35" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="35" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="35" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="35" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="35" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="35" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="35" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="35" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="35" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="35" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="35" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="35" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="35" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="54" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="54" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="35" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="35" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="35" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="35" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="35" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="35" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="35" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="35" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="35" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="35" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="35" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="35" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="35" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="35" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="35" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="35" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="35" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="35" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="15" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="66" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="66" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="41" fontId="66" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="17" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="35" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="186" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="186" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="35" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="41" fontId="17" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="41" fontId="35" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="35" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="66" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="66" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="41" fontId="15" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="35" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="35" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="35" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="35" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="35" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="35" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="35" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="35" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="179" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="179" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="179" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="179" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="179" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="177" fontId="65" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="35" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="35" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="177" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="177" fontId="35" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="35" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="65" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="35" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="35" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="65" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="65" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="65" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="35" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="35" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="35" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="35" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="35" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="35" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="35" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="35" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="35" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="35" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="35" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="35" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="35" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="35" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="54" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="54" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="177" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="177" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="177" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="177" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="177" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="35" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="35" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="35" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="35" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="35" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="35" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="35" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="35" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="35" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="35" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="35" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="35" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="35" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="35" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="35" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="35" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="35" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="35" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="15" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="177" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="177" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="177" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="177" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="65" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="65" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="177" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="177" fontId="65" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="17" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="35" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="188" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="188" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="35" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="177" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="177" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="177" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="177" fontId="17" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="177" fontId="35" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="35" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="65" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="65" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="177" fontId="15" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="35" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="35" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="35" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="35" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="35" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="35" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="35" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="35" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="182" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="182" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="182" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="182" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="182" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="182" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="44" fillId="0" borderId="14" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
@@ -7474,7 +6173,7 @@
     <xf numFmtId="0" fontId="51" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="180" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="52" fillId="22" borderId="19" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
@@ -7547,15 +6246,15 @@
     <xf numFmtId="0" fontId="52" fillId="22" borderId="19" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="178" fontId="14" fillId="0" borderId="0">
+    <xf numFmtId="177" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="178" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="181" fontId="14" fillId="0" borderId="0">
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="178" fontId="14" fillId="0" borderId="0">
+    <xf numFmtId="181" fontId="14" fillId="0" borderId="0">
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="178" fontId="18" fillId="0" borderId="0">
+    <xf numFmtId="181" fontId="18" fillId="0" borderId="0">
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="35" fillId="0" borderId="0"/>
@@ -7606,14 +6305,14 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="35" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="66" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="35" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="35" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="67" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="66" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="top"/>
       <protection locked="0"/>
     </xf>
@@ -7621,41 +6320,41 @@
       <alignment vertical="top"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="180" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="78" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="66" fillId="0" borderId="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="80" fillId="0" borderId="1"/>
+    <xf numFmtId="43" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="77" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="79" fillId="0" borderId="1"/>
   </cellStyleXfs>
   <cellXfs count="67">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="67" fillId="27" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="68" fillId="27" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="69" fillId="27" borderId="0" xfId="0" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="69" fillId="27" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="68" fillId="27" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1372" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" wrapText="1"/>
       <protection locked="0" hidden="1"/>
     </xf>
-    <xf numFmtId="8" fontId="8" fillId="0" borderId="0" xfId="1372" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="176" fontId="8" fillId="0" borderId="0" xfId="1372" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" wrapText="1"/>
       <protection locked="0" hidden="1"/>
     </xf>
-    <xf numFmtId="8" fontId="8" fillId="0" borderId="0" xfId="1372" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="176" fontId="8" fillId="0" borderId="0" xfId="1372" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0" hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="70" fillId="27" borderId="0" xfId="0" applyFont="1" applyFill="1">
+    <xf numFmtId="0" fontId="69" fillId="27" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1089" applyFont="1" applyAlignment="1">
@@ -7679,19 +6378,19 @@
     <xf numFmtId="0" fontId="53" fillId="0" borderId="0" xfId="1089" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="31" fontId="64" fillId="0" borderId="0" xfId="1089" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="31" fontId="63" fillId="0" borderId="0" xfId="1089" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="71" fillId="28" borderId="20" xfId="977" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="70" fillId="28" borderId="20" xfId="977" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="41" fontId="73" fillId="28" borderId="20" xfId="977" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="177" fontId="72" fillId="28" borderId="20" xfId="977" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="63" fillId="0" borderId="0" xfId="1089" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="1089" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="8" fontId="67" fillId="0" borderId="0" xfId="1374" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="176" fontId="66" fillId="0" borderId="0" xfId="1374" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center"/>
       <protection locked="0" hidden="1"/>
     </xf>
@@ -7701,140 +6400,140 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="75" fillId="28" borderId="20" xfId="977" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="74" fillId="28" borderId="20" xfId="977" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="214" fontId="6" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="38" fontId="6" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="214" fontId="73" fillId="28" borderId="20" xfId="977" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="65" fillId="29" borderId="21" xfId="977" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="38" fontId="72" fillId="28" borderId="20" xfId="977" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="64" fillId="29" borderId="21" xfId="977" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="65" fillId="29" borderId="22" xfId="977" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="177" fontId="64" fillId="29" borderId="22" xfId="977" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="65" fillId="29" borderId="23" xfId="977" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="177" fontId="64" fillId="29" borderId="23" xfId="977" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="65" fillId="29" borderId="24" xfId="977" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="177" fontId="64" fillId="29" borderId="24" xfId="977" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="65" fillId="29" borderId="25" xfId="977" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="177" fontId="64" fillId="29" borderId="25" xfId="977" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="213" fontId="71" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="215" fontId="70" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="41" fontId="73" fillId="28" borderId="27" xfId="977" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="177" fontId="72" fillId="28" borderId="27" xfId="977" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="214" fontId="73" fillId="28" borderId="27" xfId="977" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="83" fillId="26" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="65" fillId="28" borderId="26" xfId="977" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="38" fontId="72" fillId="28" borderId="27" xfId="977" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="81" fillId="26" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="64" fillId="28" borderId="26" xfId="977" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="65" fillId="28" borderId="8" xfId="977" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="177" fontId="64" fillId="28" borderId="8" xfId="977" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="65" fillId="28" borderId="34" xfId="977" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="177" fontId="64" fillId="28" borderId="34" xfId="977" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="85" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="83" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="84" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="82" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="80" fillId="28" borderId="20" xfId="977" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="79" fillId="28" borderId="20" xfId="977" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="88" fillId="27" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="3" fontId="85" fillId="27" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="84" fillId="0" borderId="0" xfId="1089" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="20" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="26" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="214" fontId="86" fillId="0" borderId="0" xfId="1089" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="86" fillId="0" borderId="0" xfId="1089" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="20" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="87" fillId="0" borderId="0" xfId="1089" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="87" fillId="0" borderId="0" xfId="1372" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0" hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="56" fillId="26" borderId="0" xfId="0" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="76" fillId="30" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="38" fontId="6" fillId="0" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="38" fontId="72" fillId="28" borderId="36" xfId="977" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="72" fillId="28" borderId="37" xfId="977" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="75" fillId="30" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="76" fillId="30" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="75" fillId="30" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="176" fontId="79" fillId="30" borderId="32" xfId="970" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="79" fillId="30" borderId="33" xfId="970" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="74" fillId="27" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="78" fillId="30" borderId="32" xfId="970" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="78" fillId="30" borderId="33" xfId="970" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="73" fillId="27" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="82" fillId="27" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="80" fillId="27" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="72" fillId="27" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="71" fillId="27" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="59" fillId="27" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="72" fillId="27" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="71" fillId="27" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="76" fillId="30" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="75" fillId="30" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="76" fillId="30" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="75" fillId="30" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="176" fontId="76" fillId="30" borderId="28" xfId="970" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="76" fillId="30" borderId="30" xfId="970" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="212" fontId="89" fillId="0" borderId="0" xfId="1089" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="89" fillId="0" borderId="0" xfId="1089" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="90" fillId="0" borderId="0" xfId="1089" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="90" fillId="0" borderId="0" xfId="1372" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection locked="0" hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="214" fontId="6" fillId="0" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="214" fontId="73" fillId="28" borderId="36" xfId="977" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="214" fontId="73" fillId="28" borderId="37" xfId="977" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="179" fontId="75" fillId="30" borderId="28" xfId="970" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="75" fillId="30" borderId="30" xfId="970" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -7852,8 +6551,14 @@
     <cellStyle name="_9월10일 재고리스트" xfId="11" xr:uid="{00000000-0005-0000-0000-00000A000000}"/>
     <cellStyle name="_9월17일 재고리스트" xfId="12" xr:uid="{00000000-0005-0000-0000-00000B000000}"/>
     <cellStyle name="_9월3일 주간업무" xfId="13" xr:uid="{00000000-0005-0000-0000-00000C000000}"/>
+    <cellStyle name="_고객사 제출 견전석 Sample(작업용)" xfId="102" xr:uid="{00000000-0005-0000-0000-000065000000}"/>
+    <cellStyle name="_민맥정보_데이콤_정리용_060330_조완(내부용)" xfId="103" xr:uid="{00000000-0005-0000-0000-000066000000}"/>
+    <cellStyle name="_민맥정보_데이콤-웹하드_060612_조완 (2)" xfId="104" xr:uid="{00000000-0005-0000-0000-000067000000}"/>
+    <cellStyle name="_업무 일정표-10월" xfId="105" xr:uid="{00000000-0005-0000-0000-000068000000}"/>
+    <cellStyle name="_이익초안0603(작업용)" xfId="106" xr:uid="{00000000-0005-0000-0000-000069000000}"/>
     <cellStyle name="_AP_Weekly" xfId="14" xr:uid="{00000000-0005-0000-0000-00000D000000}"/>
     <cellStyle name="_Ap1x_SGVN-2002_04-Tracy" xfId="15" xr:uid="{00000000-0005-0000-0000-00000E000000}"/>
+    <cellStyle name="_Ap1x_SGVN-2002_04-Tracy_복KR Q106 DPFR Computation(13feb06AP)_DL_HJ" xfId="30" xr:uid="{00000000-0005-0000-0000-00001D000000}"/>
     <cellStyle name="_Ap1x_SGVN-2002_04-Tracy_Book1" xfId="16" xr:uid="{00000000-0005-0000-0000-00000F000000}"/>
     <cellStyle name="_Ap1x_SGVN-2002_04-Tracy_Book3" xfId="17" xr:uid="{00000000-0005-0000-0000-000010000000}"/>
     <cellStyle name="_Ap1x_SGVN-2002_04-Tracy_FY05 1H CS Quota Deployment Exercise" xfId="18" xr:uid="{00000000-0005-0000-0000-000011000000}"/>
@@ -7862,14 +6567,14 @@
     <cellStyle name="_Ap1x_SGVN-2002_04-Tracy_Korea give Q405 DPFR Template(use BO data) " xfId="21" xr:uid="{00000000-0005-0000-0000-000014000000}"/>
     <cellStyle name="_Ap1x_SGVN-2002_04-Tracy_KR Q106 DPFR Computation (13feb06)" xfId="22" xr:uid="{00000000-0005-0000-0000-000015000000}"/>
     <cellStyle name="_Ap1x_SGVN-2002_04-Tracy_Q106 DPFR Template_Korea(5)(实验版本)" xfId="23" xr:uid="{00000000-0005-0000-0000-000016000000}"/>
+    <cellStyle name="_Ap1x_SGVN-2002_04-Tracy_Q405 DPFR Computation_v4 (3) final last " xfId="25" xr:uid="{00000000-0005-0000-0000-000018000000}"/>
     <cellStyle name="_Ap1x_SGVN-2002_04-Tracy_Q405 DPFR Computation(Final last)  " xfId="24" xr:uid="{00000000-0005-0000-0000-000017000000}"/>
-    <cellStyle name="_Ap1x_SGVN-2002_04-Tracy_Q405 DPFR Computation_v4 (3) final last " xfId="25" xr:uid="{00000000-0005-0000-0000-000018000000}"/>
     <cellStyle name="_Ap1x_SGVN-2002_04-Tracy_Q405 DPFR Template_Korno bulk orderingea (2)" xfId="26" xr:uid="{00000000-0005-0000-0000-000019000000}"/>
     <cellStyle name="_Ap1x_SGVN-2002_04-Tracy_Q405 DPFR Template_Korno bulk orderingea (3)" xfId="27" xr:uid="{00000000-0005-0000-0000-00001A000000}"/>
     <cellStyle name="_Ap1x_SGVN-2002_04-Tracy_Q405 DPFR Template_Korno bulk orderingea (4)" xfId="28" xr:uid="{00000000-0005-0000-0000-00001B000000}"/>
     <cellStyle name="_Ap1x_SGVN-2002_04-Tracy_Taiwan1" xfId="29" xr:uid="{00000000-0005-0000-0000-00001C000000}"/>
-    <cellStyle name="_Ap1x_SGVN-2002_04-Tracy_복KR Q106 DPFR Computation(13feb06AP)_DL_HJ" xfId="30" xr:uid="{00000000-0005-0000-0000-00001D000000}"/>
     <cellStyle name="_APJ_SPO_Perf_Report_151205" xfId="31" xr:uid="{00000000-0005-0000-0000-00001E000000}"/>
+    <cellStyle name="_APJ_SPO_Perf_Report_151205_복KR Q106 DPFR Computation(13feb06AP)_DL_HJ" xfId="44" xr:uid="{00000000-0005-0000-0000-00002B000000}"/>
     <cellStyle name="_APJ_SPO_Perf_Report_151205_Book1" xfId="32" xr:uid="{00000000-0005-0000-0000-00001F000000}"/>
     <cellStyle name="_APJ_SPO_Perf_Report_151205_Book3" xfId="33" xr:uid="{00000000-0005-0000-0000-000020000000}"/>
     <cellStyle name="_APJ_SPO_Perf_Report_151205_Korea give Q106 DPFR Computation template(2)" xfId="34" xr:uid="{00000000-0005-0000-0000-000021000000}"/>
@@ -7877,15 +6582,15 @@
     <cellStyle name="_APJ_SPO_Perf_Report_151205_Korea give Q405 DPFR Template(use BO data) " xfId="36" xr:uid="{00000000-0005-0000-0000-000023000000}"/>
     <cellStyle name="_APJ_SPO_Perf_Report_151205_KR Q106 DPFR Computation (13feb06)" xfId="37" xr:uid="{00000000-0005-0000-0000-000024000000}"/>
     <cellStyle name="_APJ_SPO_Perf_Report_151205_Q106 DPFR Template_Korea(5)(实验版本)" xfId="38" xr:uid="{00000000-0005-0000-0000-000025000000}"/>
+    <cellStyle name="_APJ_SPO_Perf_Report_151205_Q405 DPFR Computation_v4 (3) final last " xfId="40" xr:uid="{00000000-0005-0000-0000-000027000000}"/>
     <cellStyle name="_APJ_SPO_Perf_Report_151205_Q405 DPFR Computation(Final last)  " xfId="39" xr:uid="{00000000-0005-0000-0000-000026000000}"/>
-    <cellStyle name="_APJ_SPO_Perf_Report_151205_Q405 DPFR Computation_v4 (3) final last " xfId="40" xr:uid="{00000000-0005-0000-0000-000027000000}"/>
     <cellStyle name="_APJ_SPO_Perf_Report_151205_Q405 DPFR Template_Korno bulk orderingea (2)" xfId="41" xr:uid="{00000000-0005-0000-0000-000028000000}"/>
     <cellStyle name="_APJ_SPO_Perf_Report_151205_Q405 DPFR Template_Korno bulk orderingea (3)" xfId="42" xr:uid="{00000000-0005-0000-0000-000029000000}"/>
     <cellStyle name="_APJ_SPO_Perf_Report_151205_Q405 DPFR Template_Korno bulk orderingea (4)" xfId="43" xr:uid="{00000000-0005-0000-0000-00002A000000}"/>
-    <cellStyle name="_APJ_SPO_Perf_Report_151205_복KR Q106 DPFR Computation(13feb06AP)_DL_HJ" xfId="44" xr:uid="{00000000-0005-0000-0000-00002B000000}"/>
     <cellStyle name="_Comm-Ent Quota and Booking Rules" xfId="45" xr:uid="{00000000-0005-0000-0000-00002C000000}"/>
     <cellStyle name="_FIN 재고관리" xfId="46" xr:uid="{00000000-0005-0000-0000-00002D000000}"/>
     <cellStyle name="_manual Adjustments" xfId="47" xr:uid="{00000000-0005-0000-0000-00002E000000}"/>
+    <cellStyle name="_manual Adjustments_복KR Q106 DPFR Computation(13feb06AP)_DL_HJ" xfId="60" xr:uid="{00000000-0005-0000-0000-00003B000000}"/>
     <cellStyle name="_manual Adjustments_Book1" xfId="48" xr:uid="{00000000-0005-0000-0000-00002F000000}"/>
     <cellStyle name="_manual Adjustments_Book3" xfId="49" xr:uid="{00000000-0005-0000-0000-000030000000}"/>
     <cellStyle name="_manual Adjustments_Korea give Q106 DPFR Computation template(2)" xfId="50" xr:uid="{00000000-0005-0000-0000-000031000000}"/>
@@ -7893,12 +6598,11 @@
     <cellStyle name="_manual Adjustments_Korea give Q405 DPFR Template(use BO data) " xfId="52" xr:uid="{00000000-0005-0000-0000-000033000000}"/>
     <cellStyle name="_manual Adjustments_KR Q106 DPFR Computation (13feb06)" xfId="53" xr:uid="{00000000-0005-0000-0000-000034000000}"/>
     <cellStyle name="_manual Adjustments_Q106 DPFR Template_Korea(5)(实验版本)" xfId="54" xr:uid="{00000000-0005-0000-0000-000035000000}"/>
+    <cellStyle name="_manual Adjustments_Q405 DPFR Computation_v4 (3) final last " xfId="56" xr:uid="{00000000-0005-0000-0000-000037000000}"/>
     <cellStyle name="_manual Adjustments_Q405 DPFR Computation(Final last)  " xfId="55" xr:uid="{00000000-0005-0000-0000-000036000000}"/>
-    <cellStyle name="_manual Adjustments_Q405 DPFR Computation_v4 (3) final last " xfId="56" xr:uid="{00000000-0005-0000-0000-000037000000}"/>
     <cellStyle name="_manual Adjustments_Q405 DPFR Template_Korno bulk orderingea (2)" xfId="57" xr:uid="{00000000-0005-0000-0000-000038000000}"/>
     <cellStyle name="_manual Adjustments_Q405 DPFR Template_Korno bulk orderingea (3)" xfId="58" xr:uid="{00000000-0005-0000-0000-000039000000}"/>
     <cellStyle name="_manual Adjustments_Q405 DPFR Template_Korno bulk orderingea (4)" xfId="59" xr:uid="{00000000-0005-0000-0000-00003A000000}"/>
-    <cellStyle name="_manual Adjustments_복KR Q106 DPFR Computation(13feb06AP)_DL_HJ" xfId="60" xr:uid="{00000000-0005-0000-0000-00003B000000}"/>
     <cellStyle name="_NFQ020419_1(유경화)" xfId="61" xr:uid="{00000000-0005-0000-0000-00003C000000}"/>
     <cellStyle name="_Quota" xfId="62" xr:uid="{00000000-0005-0000-0000-00003D000000}"/>
     <cellStyle name="_Quota_1" xfId="63" xr:uid="{00000000-0005-0000-0000-00003E000000}"/>
@@ -7906,6 +6610,7 @@
     <cellStyle name="_Raw" xfId="65" xr:uid="{00000000-0005-0000-0000-000040000000}"/>
     <cellStyle name="_RAW Data" xfId="66" xr:uid="{00000000-0005-0000-0000-000041000000}"/>
     <cellStyle name="_Revenue_goal" xfId="67" xr:uid="{00000000-0005-0000-0000-000042000000}"/>
+    <cellStyle name="_Revenue_goal_복KR Q106 DPFR Computation(13feb06AP)_DL_HJ" xfId="82" xr:uid="{00000000-0005-0000-0000-000051000000}"/>
     <cellStyle name="_Revenue_goal_Book1" xfId="68" xr:uid="{00000000-0005-0000-0000-000043000000}"/>
     <cellStyle name="_Revenue_goal_Book3" xfId="69" xr:uid="{00000000-0005-0000-0000-000044000000}"/>
     <cellStyle name="_Revenue_goal_FY05 1H CS Quota Deployment Exercise" xfId="70" xr:uid="{00000000-0005-0000-0000-000045000000}"/>
@@ -7914,16 +6619,16 @@
     <cellStyle name="_Revenue_goal_Korea give Q405 DPFR Template(use BO data) " xfId="73" xr:uid="{00000000-0005-0000-0000-000048000000}"/>
     <cellStyle name="_Revenue_goal_KR Q106 DPFR Computation (13feb06)" xfId="74" xr:uid="{00000000-0005-0000-0000-000049000000}"/>
     <cellStyle name="_Revenue_goal_Q106 DPFR Template_Korea(5)(实验版本)" xfId="75" xr:uid="{00000000-0005-0000-0000-00004A000000}"/>
+    <cellStyle name="_Revenue_goal_Q405 DPFR Computation_v4 (3) final last " xfId="77" xr:uid="{00000000-0005-0000-0000-00004C000000}"/>
     <cellStyle name="_Revenue_goal_Q405 DPFR Computation(Final last)  " xfId="76" xr:uid="{00000000-0005-0000-0000-00004B000000}"/>
-    <cellStyle name="_Revenue_goal_Q405 DPFR Computation_v4 (3) final last " xfId="77" xr:uid="{00000000-0005-0000-0000-00004C000000}"/>
     <cellStyle name="_Revenue_goal_Q405 DPFR Template_Korno bulk orderingea (2)" xfId="78" xr:uid="{00000000-0005-0000-0000-00004D000000}"/>
     <cellStyle name="_Revenue_goal_Q405 DPFR Template_Korno bulk orderingea (3)" xfId="79" xr:uid="{00000000-0005-0000-0000-00004E000000}"/>
     <cellStyle name="_Revenue_goal_Q405 DPFR Template_Korno bulk orderingea (4)" xfId="80" xr:uid="{00000000-0005-0000-0000-00004F000000}"/>
     <cellStyle name="_Revenue_goal_Taiwan1" xfId="81" xr:uid="{00000000-0005-0000-0000-000050000000}"/>
-    <cellStyle name="_Revenue_goal_복KR Q106 DPFR Computation(13feb06AP)_DL_HJ" xfId="82" xr:uid="{00000000-0005-0000-0000-000051000000}"/>
     <cellStyle name="_SGBU Partners List - OSRM" xfId="83" xr:uid="{00000000-0005-0000-0000-000052000000}"/>
     <cellStyle name="_SPO 30Oct (2)" xfId="84" xr:uid="{00000000-0005-0000-0000-000053000000}"/>
     <cellStyle name="_SPO Q4" xfId="85" xr:uid="{00000000-0005-0000-0000-000054000000}"/>
+    <cellStyle name="_SPO Q4_복KR Q106 DPFR Computation(13feb06AP)_DL_HJ" xfId="98" xr:uid="{00000000-0005-0000-0000-000061000000}"/>
     <cellStyle name="_SPO Q4_Book1" xfId="86" xr:uid="{00000000-0005-0000-0000-000055000000}"/>
     <cellStyle name="_SPO Q4_Book3" xfId="87" xr:uid="{00000000-0005-0000-0000-000056000000}"/>
     <cellStyle name="_SPO Q4_Korea give Q106 DPFR Computation template(2)" xfId="88" xr:uid="{00000000-0005-0000-0000-000057000000}"/>
@@ -7931,20 +6636,14 @@
     <cellStyle name="_SPO Q4_Korea give Q405 DPFR Template(use BO data) " xfId="90" xr:uid="{00000000-0005-0000-0000-000059000000}"/>
     <cellStyle name="_SPO Q4_KR Q106 DPFR Computation (13feb06)" xfId="91" xr:uid="{00000000-0005-0000-0000-00005A000000}"/>
     <cellStyle name="_SPO Q4_Q106 DPFR Template_Korea(5)(实验版本)" xfId="92" xr:uid="{00000000-0005-0000-0000-00005B000000}"/>
+    <cellStyle name="_SPO Q4_Q405 DPFR Computation_v4 (3) final last " xfId="94" xr:uid="{00000000-0005-0000-0000-00005D000000}"/>
     <cellStyle name="_SPO Q4_Q405 DPFR Computation(Final last)  " xfId="93" xr:uid="{00000000-0005-0000-0000-00005C000000}"/>
-    <cellStyle name="_SPO Q4_Q405 DPFR Computation_v4 (3) final last " xfId="94" xr:uid="{00000000-0005-0000-0000-00005D000000}"/>
     <cellStyle name="_SPO Q4_Q405 DPFR Template_Korno bulk orderingea (2)" xfId="95" xr:uid="{00000000-0005-0000-0000-00005E000000}"/>
     <cellStyle name="_SPO Q4_Q405 DPFR Template_Korno bulk orderingea (3)" xfId="96" xr:uid="{00000000-0005-0000-0000-00005F000000}"/>
     <cellStyle name="_SPO Q4_Q405 DPFR Template_Korno bulk orderingea (4)" xfId="97" xr:uid="{00000000-0005-0000-0000-000060000000}"/>
-    <cellStyle name="_SPO Q4_복KR Q106 DPFR Computation(13feb06AP)_DL_HJ" xfId="98" xr:uid="{00000000-0005-0000-0000-000061000000}"/>
     <cellStyle name="_SPO REPORTING FORMAT 2H05 (2)" xfId="99" xr:uid="{00000000-0005-0000-0000-000062000000}"/>
     <cellStyle name="_SPO review FY05-1H-1220 (3)" xfId="100" xr:uid="{00000000-0005-0000-0000-000063000000}"/>
     <cellStyle name="_spo_total_daily20050713 2" xfId="101" xr:uid="{00000000-0005-0000-0000-000064000000}"/>
-    <cellStyle name="_고객사 제출 견전석 Sample(작업용)" xfId="102" xr:uid="{00000000-0005-0000-0000-000065000000}"/>
-    <cellStyle name="_민맥정보_데이콤_정리용_060330_조완(내부용)" xfId="103" xr:uid="{00000000-0005-0000-0000-000066000000}"/>
-    <cellStyle name="_민맥정보_데이콤-웹하드_060612_조완 (2)" xfId="104" xr:uid="{00000000-0005-0000-0000-000067000000}"/>
-    <cellStyle name="_업무 일정표-10월" xfId="105" xr:uid="{00000000-0005-0000-0000-000068000000}"/>
-    <cellStyle name="_이익초안0603(작업용)" xfId="106" xr:uid="{00000000-0005-0000-0000-000069000000}"/>
     <cellStyle name="=C:\WINNT\SYSTEM32\COMMAND.COM" xfId="107" xr:uid="{00000000-0005-0000-0000-00006A000000}"/>
     <cellStyle name="0 decimals" xfId="108" xr:uid="{00000000-0005-0000-0000-00006B000000}"/>
     <cellStyle name="0,0_x000d__x000a_NA_x000d__x000a_" xfId="109" xr:uid="{00000000-0005-0000-0000-00006C000000}"/>
@@ -8382,113 +7081,6 @@
     <cellStyle name="60% - 강조색6 7" xfId="541" xr:uid="{00000000-0005-0000-0000-00001C020000}"/>
     <cellStyle name="60% - 강조색6 8" xfId="542" xr:uid="{00000000-0005-0000-0000-00001D020000}"/>
     <cellStyle name="60% - 강조색6 9" xfId="543" xr:uid="{00000000-0005-0000-0000-00001E020000}"/>
-    <cellStyle name="C:\Data\MS\Excel" xfId="544" xr:uid="{00000000-0005-0000-0000-00001F020000}"/>
-    <cellStyle name="Calc" xfId="545" xr:uid="{00000000-0005-0000-0000-000020020000}"/>
-    <cellStyle name="Calc Currency (0)" xfId="546" xr:uid="{00000000-0005-0000-0000-000021020000}"/>
-    <cellStyle name="Calc Currency (2)" xfId="547" xr:uid="{00000000-0005-0000-0000-000022020000}"/>
-    <cellStyle name="Calc Percent (0)" xfId="548" xr:uid="{00000000-0005-0000-0000-000023020000}"/>
-    <cellStyle name="Calc Percent (1)" xfId="549" xr:uid="{00000000-0005-0000-0000-000024020000}"/>
-    <cellStyle name="Calc Percent (2)" xfId="550" xr:uid="{00000000-0005-0000-0000-000025020000}"/>
-    <cellStyle name="Calc Units (0)" xfId="551" xr:uid="{00000000-0005-0000-0000-000026020000}"/>
-    <cellStyle name="Calc Units (1)" xfId="552" xr:uid="{00000000-0005-0000-0000-000027020000}"/>
-    <cellStyle name="Calc Units (2)" xfId="553" xr:uid="{00000000-0005-0000-0000-000028020000}"/>
-    <cellStyle name="Calc_Book1" xfId="554" xr:uid="{00000000-0005-0000-0000-000029020000}"/>
-    <cellStyle name="category" xfId="555" xr:uid="{00000000-0005-0000-0000-00002A020000}"/>
-    <cellStyle name="Comma" xfId="556" xr:uid="{00000000-0005-0000-0000-00002B020000}"/>
-    <cellStyle name="Comma  - Style1" xfId="557" xr:uid="{00000000-0005-0000-0000-00002C020000}"/>
-    <cellStyle name="Comma  - Style2" xfId="558" xr:uid="{00000000-0005-0000-0000-00002D020000}"/>
-    <cellStyle name="Comma  - Style3" xfId="559" xr:uid="{00000000-0005-0000-0000-00002E020000}"/>
-    <cellStyle name="Comma  - Style4" xfId="560" xr:uid="{00000000-0005-0000-0000-00002F020000}"/>
-    <cellStyle name="Comma  - Style5" xfId="561" xr:uid="{00000000-0005-0000-0000-000030020000}"/>
-    <cellStyle name="Comma  - Style6" xfId="562" xr:uid="{00000000-0005-0000-0000-000031020000}"/>
-    <cellStyle name="Comma  - Style7" xfId="563" xr:uid="{00000000-0005-0000-0000-000032020000}"/>
-    <cellStyle name="Comma  - Style8" xfId="564" xr:uid="{00000000-0005-0000-0000-000033020000}"/>
-    <cellStyle name="Comma [0] 4" xfId="565" xr:uid="{00000000-0005-0000-0000-000034020000}"/>
-    <cellStyle name="Comma [0] 4 2" xfId="566" xr:uid="{00000000-0005-0000-0000-000035020000}"/>
-    <cellStyle name="Comma [0] 4 3" xfId="567" xr:uid="{00000000-0005-0000-0000-000036020000}"/>
-    <cellStyle name="Comma [0]_ SG&amp;A Bridge " xfId="568" xr:uid="{00000000-0005-0000-0000-000037020000}"/>
-    <cellStyle name="Comma [00]" xfId="569" xr:uid="{00000000-0005-0000-0000-000038020000}"/>
-    <cellStyle name="Comma_ SG&amp;A Bridge " xfId="570" xr:uid="{00000000-0005-0000-0000-000039020000}"/>
-    <cellStyle name="Currency" xfId="571" xr:uid="{00000000-0005-0000-0000-00003A020000}"/>
-    <cellStyle name="Currency [0]_ SG&amp;A Bridge " xfId="572" xr:uid="{00000000-0005-0000-0000-00003B020000}"/>
-    <cellStyle name="Currency [00]" xfId="573" xr:uid="{00000000-0005-0000-0000-00003C020000}"/>
-    <cellStyle name="Currency_ SG&amp;A Bridge " xfId="574" xr:uid="{00000000-0005-0000-0000-00003D020000}"/>
-    <cellStyle name="Date" xfId="575" xr:uid="{00000000-0005-0000-0000-00003E020000}"/>
-    <cellStyle name="Date Short" xfId="576" xr:uid="{00000000-0005-0000-0000-00003F020000}"/>
-    <cellStyle name="date_Book1" xfId="577" xr:uid="{00000000-0005-0000-0000-000040020000}"/>
-    <cellStyle name="DELTA" xfId="578" xr:uid="{00000000-0005-0000-0000-000041020000}"/>
-    <cellStyle name="discount" xfId="579" xr:uid="{00000000-0005-0000-0000-000042020000}"/>
-    <cellStyle name="Enter Currency (0)" xfId="580" xr:uid="{00000000-0005-0000-0000-000043020000}"/>
-    <cellStyle name="Enter Currency (2)" xfId="581" xr:uid="{00000000-0005-0000-0000-000044020000}"/>
-    <cellStyle name="Enter Units (0)" xfId="582" xr:uid="{00000000-0005-0000-0000-000045020000}"/>
-    <cellStyle name="Enter Units (1)" xfId="583" xr:uid="{00000000-0005-0000-0000-000046020000}"/>
-    <cellStyle name="Enter Units (2)" xfId="584" xr:uid="{00000000-0005-0000-0000-000047020000}"/>
-    <cellStyle name="First" xfId="585" xr:uid="{00000000-0005-0000-0000-000048020000}"/>
-    <cellStyle name="Fixed" xfId="586" xr:uid="{00000000-0005-0000-0000-000049020000}"/>
-    <cellStyle name="Grey" xfId="587" xr:uid="{00000000-0005-0000-0000-00004A020000}"/>
-    <cellStyle name="HEADER" xfId="588" xr:uid="{00000000-0005-0000-0000-00004B020000}"/>
-    <cellStyle name="Header1" xfId="589" xr:uid="{00000000-0005-0000-0000-00004C020000}"/>
-    <cellStyle name="Header2" xfId="590" xr:uid="{00000000-0005-0000-0000-00004D020000}"/>
-    <cellStyle name="Heading1" xfId="591" xr:uid="{00000000-0005-0000-0000-00004E020000}"/>
-    <cellStyle name="Heading2" xfId="592" xr:uid="{00000000-0005-0000-0000-00004F020000}"/>
-    <cellStyle name="Hyperlink" xfId="593" xr:uid="{00000000-0005-0000-0000-000050020000}"/>
-    <cellStyle name="Input [yellow]" xfId="594" xr:uid="{00000000-0005-0000-0000-000051020000}"/>
-    <cellStyle name="Jun" xfId="595" xr:uid="{00000000-0005-0000-0000-000052020000}"/>
-    <cellStyle name="Komma [0]_BINV" xfId="596" xr:uid="{00000000-0005-0000-0000-000053020000}"/>
-    <cellStyle name="Komma_BINV" xfId="597" xr:uid="{00000000-0005-0000-0000-000054020000}"/>
-    <cellStyle name="Link Currency (0)" xfId="598" xr:uid="{00000000-0005-0000-0000-000055020000}"/>
-    <cellStyle name="Link Currency (2)" xfId="599" xr:uid="{00000000-0005-0000-0000-000056020000}"/>
-    <cellStyle name="Link Units (0)" xfId="600" xr:uid="{00000000-0005-0000-0000-000057020000}"/>
-    <cellStyle name="Link Units (1)" xfId="601" xr:uid="{00000000-0005-0000-0000-000058020000}"/>
-    <cellStyle name="Link Units (2)" xfId="602" xr:uid="{00000000-0005-0000-0000-000059020000}"/>
-    <cellStyle name="Millares [0]_laroux" xfId="603" xr:uid="{00000000-0005-0000-0000-00005A020000}"/>
-    <cellStyle name="Millares_laroux" xfId="604" xr:uid="{00000000-0005-0000-0000-00005B020000}"/>
-    <cellStyle name="Milliers [0]_EDYAN" xfId="605" xr:uid="{00000000-0005-0000-0000-00005C020000}"/>
-    <cellStyle name="Milliers_EDYAN" xfId="606" xr:uid="{00000000-0005-0000-0000-00005D020000}"/>
-    <cellStyle name="Model" xfId="607" xr:uid="{00000000-0005-0000-0000-00005E020000}"/>
-    <cellStyle name="Moneda [0]_laroux" xfId="608" xr:uid="{00000000-0005-0000-0000-00005F020000}"/>
-    <cellStyle name="Moneda_laroux" xfId="609" xr:uid="{00000000-0005-0000-0000-000060020000}"/>
-    <cellStyle name="Monétaire [0]_EDYAN" xfId="610" xr:uid="{00000000-0005-0000-0000-000061020000}"/>
-    <cellStyle name="Monétaire_EDYAN" xfId="611" xr:uid="{00000000-0005-0000-0000-000062020000}"/>
-    <cellStyle name="Normal - Style1" xfId="612" xr:uid="{00000000-0005-0000-0000-000063020000}"/>
-    <cellStyle name="Normal 1" xfId="613" xr:uid="{00000000-0005-0000-0000-000064020000}"/>
-    <cellStyle name="Normal 2" xfId="614" xr:uid="{00000000-0005-0000-0000-000065020000}"/>
-    <cellStyle name="Normal 2 3" xfId="615" xr:uid="{00000000-0005-0000-0000-000066020000}"/>
-    <cellStyle name="Normal 2_Compatibility Matrix" xfId="1379" xr:uid="{00000000-0005-0000-0000-000067020000}"/>
-    <cellStyle name="Normal 4" xfId="616" xr:uid="{00000000-0005-0000-0000-000068020000}"/>
-    <cellStyle name="Normal 4 18" xfId="617" xr:uid="{00000000-0005-0000-0000-000069020000}"/>
-    <cellStyle name="Normal_ SG&amp;A Bridge " xfId="618" xr:uid="{00000000-0005-0000-0000-00006A020000}"/>
-    <cellStyle name="Numk" xfId="619" xr:uid="{00000000-0005-0000-0000-00006B020000}"/>
-    <cellStyle name="NWS" xfId="620" xr:uid="{00000000-0005-0000-0000-00006C020000}"/>
-    <cellStyle name="OneDecPer" xfId="621" xr:uid="{00000000-0005-0000-0000-00006D020000}"/>
-    <cellStyle name="Percent" xfId="622" xr:uid="{00000000-0005-0000-0000-00006E020000}"/>
-    <cellStyle name="Percent [0]" xfId="623" xr:uid="{00000000-0005-0000-0000-00006F020000}"/>
-    <cellStyle name="Percent [00]" xfId="624" xr:uid="{00000000-0005-0000-0000-000070020000}"/>
-    <cellStyle name="Percent [2]" xfId="625" xr:uid="{00000000-0005-0000-0000-000071020000}"/>
-    <cellStyle name="Percent_#6 Temps &amp; Contractors" xfId="626" xr:uid="{00000000-0005-0000-0000-000072020000}"/>
-    <cellStyle name="PrePop Currency (0)" xfId="627" xr:uid="{00000000-0005-0000-0000-000073020000}"/>
-    <cellStyle name="PrePop Currency (2)" xfId="628" xr:uid="{00000000-0005-0000-0000-000074020000}"/>
-    <cellStyle name="PrePop Units (0)" xfId="629" xr:uid="{00000000-0005-0000-0000-000075020000}"/>
-    <cellStyle name="PrePop Units (1)" xfId="630" xr:uid="{00000000-0005-0000-0000-000076020000}"/>
-    <cellStyle name="PrePop Units (2)" xfId="631" xr:uid="{00000000-0005-0000-0000-000077020000}"/>
-    <cellStyle name="Prices" xfId="632" xr:uid="{00000000-0005-0000-0000-000078020000}"/>
-    <cellStyle name="Procent_BINV" xfId="633" xr:uid="{00000000-0005-0000-0000-000079020000}"/>
-    <cellStyle name="protected" xfId="634" xr:uid="{00000000-0005-0000-0000-00007A020000}"/>
-    <cellStyle name="PSChar" xfId="635" xr:uid="{00000000-0005-0000-0000-00007B020000}"/>
-    <cellStyle name="red" xfId="636" xr:uid="{00000000-0005-0000-0000-00007C020000}"/>
-    <cellStyle name="Standaard_BINV" xfId="637" xr:uid="{00000000-0005-0000-0000-00007D020000}"/>
-    <cellStyle name="Standard_Tabelle1" xfId="638" xr:uid="{00000000-0005-0000-0000-00007E020000}"/>
-    <cellStyle name="Style 1" xfId="639" xr:uid="{00000000-0005-0000-0000-00007F020000}"/>
-    <cellStyle name="subhead" xfId="640" xr:uid="{00000000-0005-0000-0000-000080020000}"/>
-    <cellStyle name="Text Indent A" xfId="641" xr:uid="{00000000-0005-0000-0000-000081020000}"/>
-    <cellStyle name="Text Indent B" xfId="642" xr:uid="{00000000-0005-0000-0000-000082020000}"/>
-    <cellStyle name="Text Indent C" xfId="643" xr:uid="{00000000-0005-0000-0000-000083020000}"/>
-    <cellStyle name="Total" xfId="644" xr:uid="{00000000-0005-0000-0000-000084020000}"/>
-    <cellStyle name="Trend_title1" xfId="645" xr:uid="{00000000-0005-0000-0000-000085020000}"/>
-    <cellStyle name="Try1" xfId="646" xr:uid="{00000000-0005-0000-0000-000086020000}"/>
-    <cellStyle name="unprotected" xfId="647" xr:uid="{00000000-0005-0000-0000-000087020000}"/>
-    <cellStyle name="Valuta [0]_BINV" xfId="648" xr:uid="{00000000-0005-0000-0000-000088020000}"/>
-    <cellStyle name="Valuta_BINV" xfId="649" xr:uid="{00000000-0005-0000-0000-000089020000}"/>
     <cellStyle name="강조색1 10" xfId="650" xr:uid="{00000000-0005-0000-0000-00008A020000}"/>
     <cellStyle name="강조색1 11" xfId="651" xr:uid="{00000000-0005-0000-0000-00008B020000}"/>
     <cellStyle name="강조색1 12" xfId="652" xr:uid="{00000000-0005-0000-0000-00008C020000}"/>
@@ -9219,6 +7811,113 @@
     <cellStyle name="하이퍼링크" xfId="1374" builtinId="8"/>
     <cellStyle name="하이퍼링크 2" xfId="1375" xr:uid="{00000000-0005-0000-0000-000062050000}"/>
     <cellStyle name="桁区切り [0.00]_Q201 FDE - CKK" xfId="1376" xr:uid="{00000000-0005-0000-0000-000063050000}"/>
+    <cellStyle name="C:\Data\MS\Excel" xfId="544" xr:uid="{00000000-0005-0000-0000-00001F020000}"/>
+    <cellStyle name="Calc" xfId="545" xr:uid="{00000000-0005-0000-0000-000020020000}"/>
+    <cellStyle name="Calc Currency (0)" xfId="546" xr:uid="{00000000-0005-0000-0000-000021020000}"/>
+    <cellStyle name="Calc Currency (2)" xfId="547" xr:uid="{00000000-0005-0000-0000-000022020000}"/>
+    <cellStyle name="Calc Percent (0)" xfId="548" xr:uid="{00000000-0005-0000-0000-000023020000}"/>
+    <cellStyle name="Calc Percent (1)" xfId="549" xr:uid="{00000000-0005-0000-0000-000024020000}"/>
+    <cellStyle name="Calc Percent (2)" xfId="550" xr:uid="{00000000-0005-0000-0000-000025020000}"/>
+    <cellStyle name="Calc Units (0)" xfId="551" xr:uid="{00000000-0005-0000-0000-000026020000}"/>
+    <cellStyle name="Calc Units (1)" xfId="552" xr:uid="{00000000-0005-0000-0000-000027020000}"/>
+    <cellStyle name="Calc Units (2)" xfId="553" xr:uid="{00000000-0005-0000-0000-000028020000}"/>
+    <cellStyle name="Calc_Book1" xfId="554" xr:uid="{00000000-0005-0000-0000-000029020000}"/>
+    <cellStyle name="category" xfId="555" xr:uid="{00000000-0005-0000-0000-00002A020000}"/>
+    <cellStyle name="Comma" xfId="556" xr:uid="{00000000-0005-0000-0000-00002B020000}"/>
+    <cellStyle name="Comma  - Style1" xfId="557" xr:uid="{00000000-0005-0000-0000-00002C020000}"/>
+    <cellStyle name="Comma  - Style2" xfId="558" xr:uid="{00000000-0005-0000-0000-00002D020000}"/>
+    <cellStyle name="Comma  - Style3" xfId="559" xr:uid="{00000000-0005-0000-0000-00002E020000}"/>
+    <cellStyle name="Comma  - Style4" xfId="560" xr:uid="{00000000-0005-0000-0000-00002F020000}"/>
+    <cellStyle name="Comma  - Style5" xfId="561" xr:uid="{00000000-0005-0000-0000-000030020000}"/>
+    <cellStyle name="Comma  - Style6" xfId="562" xr:uid="{00000000-0005-0000-0000-000031020000}"/>
+    <cellStyle name="Comma  - Style7" xfId="563" xr:uid="{00000000-0005-0000-0000-000032020000}"/>
+    <cellStyle name="Comma  - Style8" xfId="564" xr:uid="{00000000-0005-0000-0000-000033020000}"/>
+    <cellStyle name="Comma [0] 4" xfId="565" xr:uid="{00000000-0005-0000-0000-000034020000}"/>
+    <cellStyle name="Comma [0] 4 2" xfId="566" xr:uid="{00000000-0005-0000-0000-000035020000}"/>
+    <cellStyle name="Comma [0] 4 3" xfId="567" xr:uid="{00000000-0005-0000-0000-000036020000}"/>
+    <cellStyle name="Comma [0]_ SG&amp;A Bridge " xfId="568" xr:uid="{00000000-0005-0000-0000-000037020000}"/>
+    <cellStyle name="Comma [00]" xfId="569" xr:uid="{00000000-0005-0000-0000-000038020000}"/>
+    <cellStyle name="Comma_ SG&amp;A Bridge " xfId="570" xr:uid="{00000000-0005-0000-0000-000039020000}"/>
+    <cellStyle name="Currency" xfId="571" xr:uid="{00000000-0005-0000-0000-00003A020000}"/>
+    <cellStyle name="Currency [0]_ SG&amp;A Bridge " xfId="572" xr:uid="{00000000-0005-0000-0000-00003B020000}"/>
+    <cellStyle name="Currency [00]" xfId="573" xr:uid="{00000000-0005-0000-0000-00003C020000}"/>
+    <cellStyle name="Currency_ SG&amp;A Bridge " xfId="574" xr:uid="{00000000-0005-0000-0000-00003D020000}"/>
+    <cellStyle name="Date" xfId="575" xr:uid="{00000000-0005-0000-0000-00003E020000}"/>
+    <cellStyle name="Date Short" xfId="576" xr:uid="{00000000-0005-0000-0000-00003F020000}"/>
+    <cellStyle name="date_Book1" xfId="577" xr:uid="{00000000-0005-0000-0000-000040020000}"/>
+    <cellStyle name="DELTA" xfId="578" xr:uid="{00000000-0005-0000-0000-000041020000}"/>
+    <cellStyle name="discount" xfId="579" xr:uid="{00000000-0005-0000-0000-000042020000}"/>
+    <cellStyle name="Enter Currency (0)" xfId="580" xr:uid="{00000000-0005-0000-0000-000043020000}"/>
+    <cellStyle name="Enter Currency (2)" xfId="581" xr:uid="{00000000-0005-0000-0000-000044020000}"/>
+    <cellStyle name="Enter Units (0)" xfId="582" xr:uid="{00000000-0005-0000-0000-000045020000}"/>
+    <cellStyle name="Enter Units (1)" xfId="583" xr:uid="{00000000-0005-0000-0000-000046020000}"/>
+    <cellStyle name="Enter Units (2)" xfId="584" xr:uid="{00000000-0005-0000-0000-000047020000}"/>
+    <cellStyle name="First" xfId="585" xr:uid="{00000000-0005-0000-0000-000048020000}"/>
+    <cellStyle name="Fixed" xfId="586" xr:uid="{00000000-0005-0000-0000-000049020000}"/>
+    <cellStyle name="Grey" xfId="587" xr:uid="{00000000-0005-0000-0000-00004A020000}"/>
+    <cellStyle name="HEADER" xfId="588" xr:uid="{00000000-0005-0000-0000-00004B020000}"/>
+    <cellStyle name="Header1" xfId="589" xr:uid="{00000000-0005-0000-0000-00004C020000}"/>
+    <cellStyle name="Header2" xfId="590" xr:uid="{00000000-0005-0000-0000-00004D020000}"/>
+    <cellStyle name="Heading1" xfId="591" xr:uid="{00000000-0005-0000-0000-00004E020000}"/>
+    <cellStyle name="Heading2" xfId="592" xr:uid="{00000000-0005-0000-0000-00004F020000}"/>
+    <cellStyle name="Hyperlink" xfId="593" xr:uid="{00000000-0005-0000-0000-000050020000}"/>
+    <cellStyle name="Input [yellow]" xfId="594" xr:uid="{00000000-0005-0000-0000-000051020000}"/>
+    <cellStyle name="Jun" xfId="595" xr:uid="{00000000-0005-0000-0000-000052020000}"/>
+    <cellStyle name="Komma [0]_BINV" xfId="596" xr:uid="{00000000-0005-0000-0000-000053020000}"/>
+    <cellStyle name="Komma_BINV" xfId="597" xr:uid="{00000000-0005-0000-0000-000054020000}"/>
+    <cellStyle name="Link Currency (0)" xfId="598" xr:uid="{00000000-0005-0000-0000-000055020000}"/>
+    <cellStyle name="Link Currency (2)" xfId="599" xr:uid="{00000000-0005-0000-0000-000056020000}"/>
+    <cellStyle name="Link Units (0)" xfId="600" xr:uid="{00000000-0005-0000-0000-000057020000}"/>
+    <cellStyle name="Link Units (1)" xfId="601" xr:uid="{00000000-0005-0000-0000-000058020000}"/>
+    <cellStyle name="Link Units (2)" xfId="602" xr:uid="{00000000-0005-0000-0000-000059020000}"/>
+    <cellStyle name="Millares [0]_laroux" xfId="603" xr:uid="{00000000-0005-0000-0000-00005A020000}"/>
+    <cellStyle name="Millares_laroux" xfId="604" xr:uid="{00000000-0005-0000-0000-00005B020000}"/>
+    <cellStyle name="Milliers [0]_EDYAN" xfId="605" xr:uid="{00000000-0005-0000-0000-00005C020000}"/>
+    <cellStyle name="Milliers_EDYAN" xfId="606" xr:uid="{00000000-0005-0000-0000-00005D020000}"/>
+    <cellStyle name="Model" xfId="607" xr:uid="{00000000-0005-0000-0000-00005E020000}"/>
+    <cellStyle name="Moneda [0]_laroux" xfId="608" xr:uid="{00000000-0005-0000-0000-00005F020000}"/>
+    <cellStyle name="Moneda_laroux" xfId="609" xr:uid="{00000000-0005-0000-0000-000060020000}"/>
+    <cellStyle name="Monétaire [0]_EDYAN" xfId="610" xr:uid="{00000000-0005-0000-0000-000061020000}"/>
+    <cellStyle name="Monétaire_EDYAN" xfId="611" xr:uid="{00000000-0005-0000-0000-000062020000}"/>
+    <cellStyle name="Normal - Style1" xfId="612" xr:uid="{00000000-0005-0000-0000-000063020000}"/>
+    <cellStyle name="Normal 1" xfId="613" xr:uid="{00000000-0005-0000-0000-000064020000}"/>
+    <cellStyle name="Normal 2" xfId="614" xr:uid="{00000000-0005-0000-0000-000065020000}"/>
+    <cellStyle name="Normal 2 3" xfId="615" xr:uid="{00000000-0005-0000-0000-000066020000}"/>
+    <cellStyle name="Normal 2_Compatibility Matrix" xfId="1379" xr:uid="{00000000-0005-0000-0000-000067020000}"/>
+    <cellStyle name="Normal 4" xfId="616" xr:uid="{00000000-0005-0000-0000-000068020000}"/>
+    <cellStyle name="Normal 4 18" xfId="617" xr:uid="{00000000-0005-0000-0000-000069020000}"/>
+    <cellStyle name="Normal_ SG&amp;A Bridge " xfId="618" xr:uid="{00000000-0005-0000-0000-00006A020000}"/>
+    <cellStyle name="Numk" xfId="619" xr:uid="{00000000-0005-0000-0000-00006B020000}"/>
+    <cellStyle name="NWS" xfId="620" xr:uid="{00000000-0005-0000-0000-00006C020000}"/>
+    <cellStyle name="OneDecPer" xfId="621" xr:uid="{00000000-0005-0000-0000-00006D020000}"/>
+    <cellStyle name="Percent" xfId="622" xr:uid="{00000000-0005-0000-0000-00006E020000}"/>
+    <cellStyle name="Percent [0]" xfId="623" xr:uid="{00000000-0005-0000-0000-00006F020000}"/>
+    <cellStyle name="Percent [00]" xfId="624" xr:uid="{00000000-0005-0000-0000-000070020000}"/>
+    <cellStyle name="Percent [2]" xfId="625" xr:uid="{00000000-0005-0000-0000-000071020000}"/>
+    <cellStyle name="Percent_#6 Temps &amp; Contractors" xfId="626" xr:uid="{00000000-0005-0000-0000-000072020000}"/>
+    <cellStyle name="PrePop Currency (0)" xfId="627" xr:uid="{00000000-0005-0000-0000-000073020000}"/>
+    <cellStyle name="PrePop Currency (2)" xfId="628" xr:uid="{00000000-0005-0000-0000-000074020000}"/>
+    <cellStyle name="PrePop Units (0)" xfId="629" xr:uid="{00000000-0005-0000-0000-000075020000}"/>
+    <cellStyle name="PrePop Units (1)" xfId="630" xr:uid="{00000000-0005-0000-0000-000076020000}"/>
+    <cellStyle name="PrePop Units (2)" xfId="631" xr:uid="{00000000-0005-0000-0000-000077020000}"/>
+    <cellStyle name="Prices" xfId="632" xr:uid="{00000000-0005-0000-0000-000078020000}"/>
+    <cellStyle name="Procent_BINV" xfId="633" xr:uid="{00000000-0005-0000-0000-000079020000}"/>
+    <cellStyle name="protected" xfId="634" xr:uid="{00000000-0005-0000-0000-00007A020000}"/>
+    <cellStyle name="PSChar" xfId="635" xr:uid="{00000000-0005-0000-0000-00007B020000}"/>
+    <cellStyle name="red" xfId="636" xr:uid="{00000000-0005-0000-0000-00007C020000}"/>
+    <cellStyle name="Standaard_BINV" xfId="637" xr:uid="{00000000-0005-0000-0000-00007D020000}"/>
+    <cellStyle name="Standard_Tabelle1" xfId="638" xr:uid="{00000000-0005-0000-0000-00007E020000}"/>
+    <cellStyle name="Style 1" xfId="639" xr:uid="{00000000-0005-0000-0000-00007F020000}"/>
+    <cellStyle name="subhead" xfId="640" xr:uid="{00000000-0005-0000-0000-000080020000}"/>
+    <cellStyle name="Text Indent A" xfId="641" xr:uid="{00000000-0005-0000-0000-000081020000}"/>
+    <cellStyle name="Text Indent B" xfId="642" xr:uid="{00000000-0005-0000-0000-000082020000}"/>
+    <cellStyle name="Text Indent C" xfId="643" xr:uid="{00000000-0005-0000-0000-000083020000}"/>
+    <cellStyle name="Total" xfId="644" xr:uid="{00000000-0005-0000-0000-000084020000}"/>
+    <cellStyle name="Trend_title1" xfId="645" xr:uid="{00000000-0005-0000-0000-000085020000}"/>
+    <cellStyle name="Try1" xfId="646" xr:uid="{00000000-0005-0000-0000-000086020000}"/>
+    <cellStyle name="unprotected" xfId="647" xr:uid="{00000000-0005-0000-0000-000087020000}"/>
+    <cellStyle name="Valuta [0]_BINV" xfId="648" xr:uid="{00000000-0005-0000-0000-000088020000}"/>
+    <cellStyle name="Valuta_BINV" xfId="649" xr:uid="{00000000-0005-0000-0000-000089020000}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -9642,167 +8341,143 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="B1:K42"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="11.5"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="12"/>
   <cols>
-    <col min="1" max="1" width="1.08203125" style="1" customWidth="1"/>
+    <col min="1" max="1" width="1" style="1" customWidth="1"/>
     <col min="2" max="2" width="20" style="1" customWidth="1"/>
-    <col min="3" max="3" width="57.75" style="1" customWidth="1"/>
-    <col min="4" max="4" width="5.25" style="1" customWidth="1"/>
+    <col min="3" max="3" width="57.6640625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="5.1640625" style="1" customWidth="1"/>
     <col min="5" max="5" width="14.33203125" style="1" customWidth="1"/>
-    <col min="6" max="6" width="13.58203125" style="1" customWidth="1"/>
+    <col min="6" max="6" width="13.5" style="1" customWidth="1"/>
     <col min="7" max="7" width="15" style="1" customWidth="1"/>
     <col min="8" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:7" ht="12" customHeight="1">
-      <c r="B1" s="48" t="s">
+      <c r="B1" s="58" t="s">
         <v>28</v>
       </c>
-      <c r="C1" s="48"/>
-      <c r="D1" s="48"/>
-      <c r="E1" s="48"/>
-      <c r="F1" s="48"/>
-      <c r="G1" s="48"/>
+      <c r="C1" s="58"/>
+      <c r="D1" s="58"/>
+      <c r="E1" s="58"/>
+      <c r="F1" s="58"/>
+      <c r="G1" s="58"/>
     </row>
     <row r="2" spans="2:7" ht="12" customHeight="1">
-      <c r="B2" s="48"/>
-      <c r="C2" s="48"/>
-      <c r="D2" s="48"/>
-      <c r="E2" s="48"/>
-      <c r="F2" s="48"/>
-      <c r="G2" s="48"/>
+      <c r="B2" s="58"/>
+      <c r="C2" s="58"/>
+      <c r="D2" s="58"/>
+      <c r="E2" s="58"/>
+      <c r="F2" s="58"/>
+      <c r="G2" s="58"/>
     </row>
     <row r="3" spans="2:7" ht="21" customHeight="1">
-      <c r="B3" s="48"/>
-      <c r="C3" s="48"/>
-      <c r="D3" s="48"/>
-      <c r="E3" s="48"/>
-      <c r="F3" s="48"/>
-      <c r="G3" s="48"/>
+      <c r="B3" s="58"/>
+      <c r="C3" s="58"/>
+      <c r="D3" s="58"/>
+      <c r="E3" s="58"/>
+      <c r="F3" s="58"/>
+      <c r="G3" s="58"/>
     </row>
     <row r="4" spans="2:7" ht="4.5" customHeight="1"/>
     <row r="6" spans="2:7" ht="15" customHeight="1">
       <c r="B6" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="C6" s="14" t="s">
-        <v>34</v>
-      </c>
+      <c r="C6" s="14"/>
     </row>
     <row r="7" spans="2:7" ht="15" customHeight="1">
       <c r="B7" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C7" s="14" t="s">
-        <v>35</v>
-      </c>
+      <c r="C7" s="14"/>
     </row>
-    <row r="8" spans="2:7" ht="16">
+    <row r="8" spans="2:7" ht="17">
       <c r="B8" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="C8" s="59" t="s">
-        <v>41</v>
-      </c>
+      <c r="C8" s="46"/>
       <c r="E8" s="2"/>
     </row>
     <row r="9" spans="2:7" ht="15" customHeight="1">
       <c r="B9" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C9" s="59" t="s">
-        <v>42</v>
-      </c>
+      <c r="C9" s="46"/>
       <c r="E9" s="2"/>
     </row>
     <row r="10" spans="2:7" ht="15" customHeight="1">
       <c r="B10" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="C10" s="60" t="s">
-        <v>43</v>
-      </c>
-      <c r="E10" s="49" t="s">
+      <c r="C10" s="47"/>
+      <c r="E10" s="59" t="s">
         <v>31</v>
       </c>
-      <c r="F10" s="50"/>
-      <c r="G10" s="50"/>
+      <c r="F10" s="60"/>
+      <c r="G10" s="60"/>
     </row>
     <row r="11" spans="2:7" ht="16.5" customHeight="1">
       <c r="B11" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="C11" s="19" t="s">
-        <v>36</v>
-      </c>
-      <c r="E11" s="50"/>
-      <c r="F11" s="50"/>
-      <c r="G11" s="50"/>
+      <c r="C11" s="19"/>
+      <c r="E11" s="60"/>
+      <c r="F11" s="60"/>
+      <c r="G11" s="60"/>
     </row>
     <row r="12" spans="2:7" ht="16.5" customHeight="1">
       <c r="B12" s="6"/>
       <c r="C12" s="7"/>
-      <c r="E12" s="50"/>
-      <c r="F12" s="50"/>
-      <c r="G12" s="50"/>
+      <c r="E12" s="60"/>
+      <c r="F12" s="60"/>
+      <c r="G12" s="60"/>
     </row>
     <row r="13" spans="2:7" ht="14.25" customHeight="1">
       <c r="B13" s="7"/>
       <c r="C13" s="7"/>
-      <c r="E13" s="51" t="s">
+      <c r="E13" s="61" t="s">
         <v>6</v>
       </c>
-      <c r="F13" s="52"/>
-      <c r="G13" s="52"/>
+      <c r="F13" s="62"/>
+      <c r="G13" s="62"/>
     </row>
     <row r="14" spans="2:7" ht="14.25" customHeight="1">
       <c r="B14" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="C14" s="57" t="s">
-        <v>38</v>
-      </c>
+      <c r="C14" s="44"/>
       <c r="E14" s="2"/>
     </row>
     <row r="15" spans="2:7" ht="14.25" customHeight="1">
       <c r="B15" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="C15" s="15" t="s">
-        <v>37</v>
-      </c>
+      <c r="C15" s="15"/>
     </row>
     <row r="16" spans="2:7" ht="14.25" customHeight="1">
       <c r="B16" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="C16" s="58" t="s">
-        <v>39</v>
-      </c>
+      <c r="C16" s="45"/>
     </row>
     <row r="17" spans="2:11" ht="14.25" customHeight="1">
       <c r="B17" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="C17" s="18" t="s">
-        <v>40</v>
-      </c>
+      <c r="C17" s="18"/>
     </row>
     <row r="18" spans="2:11" ht="14.25" customHeight="1">
       <c r="B18" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="C18" s="18" t="s">
-        <v>32</v>
-      </c>
+      <c r="C18" s="18"/>
     </row>
     <row r="19" spans="2:11" ht="14.25" customHeight="1">
       <c r="B19" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="C19" s="41" t="s">
-        <v>44</v>
-      </c>
+      <c r="C19" s="41"/>
     </row>
     <row r="20" spans="2:11" ht="16.5" customHeight="1" thickBot="1">
       <c r="F20" s="3"/>
@@ -9810,7 +8485,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="21" spans="2:11" ht="16" thickBot="1">
+    <row r="21" spans="2:11" ht="17" thickBot="1">
       <c r="B21" s="25" t="s">
         <v>22</v>
       </c>
@@ -9830,7 +8505,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="22" spans="2:11" ht="15.5">
+    <row r="22" spans="2:11" ht="16">
       <c r="B22" s="34"/>
       <c r="C22" s="35"/>
       <c r="D22" s="35"/>
@@ -9840,94 +8515,70 @@
     </row>
     <row r="23" spans="2:11" ht="16">
       <c r="B23" s="30"/>
-      <c r="C23" s="22" t="s">
-        <v>48</v>
-      </c>
-      <c r="D23" s="39">
-        <v>1</v>
-      </c>
+      <c r="C23" s="22"/>
+      <c r="D23" s="39"/>
       <c r="E23" s="16"/>
       <c r="F23" s="17"/>
-      <c r="G23" s="31">
-        <v>3000000</v>
-      </c>
+      <c r="G23" s="31"/>
     </row>
-    <row r="24" spans="2:11" ht="129.5">
-      <c r="B24" s="38" t="s">
-        <v>49</v>
-      </c>
-      <c r="C24" s="42" t="s">
-        <v>33</v>
-      </c>
-      <c r="D24" s="21">
-        <v>1</v>
-      </c>
+    <row r="24" spans="2:11" ht="14">
+      <c r="B24" s="38"/>
+      <c r="C24" s="42"/>
+      <c r="D24" s="21"/>
       <c r="E24" s="23"/>
       <c r="F24" s="24"/>
       <c r="G24" s="32"/>
       <c r="K24" s="40"/>
     </row>
     <row r="25" spans="2:11" ht="100" customHeight="1">
-      <c r="B25" s="38" t="s">
-        <v>50</v>
-      </c>
-      <c r="C25" s="37" t="s">
-        <v>45</v>
-      </c>
-      <c r="D25" s="21">
-        <v>2</v>
-      </c>
+      <c r="B25" s="38"/>
+      <c r="C25" s="37"/>
+      <c r="D25" s="21"/>
       <c r="E25" s="23"/>
       <c r="F25" s="24"/>
       <c r="G25" s="32"/>
     </row>
     <row r="26" spans="2:11" ht="34.5" customHeight="1">
-      <c r="B26" s="38" t="s">
-        <v>51</v>
-      </c>
-      <c r="C26" s="20" t="s">
-        <v>46</v>
-      </c>
-      <c r="D26" s="21">
-        <v>1</v>
-      </c>
+      <c r="B26" s="38"/>
+      <c r="C26" s="20"/>
+      <c r="D26" s="21"/>
       <c r="E26" s="23"/>
       <c r="F26" s="24"/>
       <c r="G26" s="32"/>
     </row>
     <row r="27" spans="2:11" ht="15.5" customHeight="1" thickBot="1">
-      <c r="B27" s="61"/>
-      <c r="C27" s="62"/>
-      <c r="D27" s="63"/>
-      <c r="E27" s="64"/>
-      <c r="F27" s="65"/>
-      <c r="G27" s="66"/>
+      <c r="B27" s="48"/>
+      <c r="C27" s="49"/>
+      <c r="D27" s="50"/>
+      <c r="E27" s="51"/>
+      <c r="F27" s="52"/>
+      <c r="G27" s="53"/>
     </row>
     <row r="28" spans="2:11" ht="20.25" customHeight="1" thickBot="1">
-      <c r="B28" s="53" t="s">
+      <c r="B28" s="63" t="s">
         <v>29</v>
       </c>
-      <c r="C28" s="54"/>
-      <c r="D28" s="54"/>
-      <c r="E28" s="55">
+      <c r="C28" s="64"/>
+      <c r="D28" s="64"/>
+      <c r="E28" s="65">
         <f>SUM(G23)</f>
-        <v>3000000</v>
+        <v>0</v>
       </c>
-      <c r="F28" s="55"/>
-      <c r="G28" s="56"/>
+      <c r="F28" s="65"/>
+      <c r="G28" s="66"/>
     </row>
     <row r="29" spans="2:11" ht="20.25" customHeight="1" thickBot="1">
-      <c r="B29" s="44" t="s">
+      <c r="B29" s="54" t="s">
         <v>30</v>
       </c>
-      <c r="C29" s="45"/>
-      <c r="D29" s="45"/>
-      <c r="E29" s="46">
+      <c r="C29" s="55"/>
+      <c r="D29" s="55"/>
+      <c r="E29" s="56">
         <f>E28*1.1</f>
-        <v>3300000.0000000005</v>
+        <v>0</v>
       </c>
-      <c r="F29" s="46"/>
-      <c r="G29" s="47"/>
+      <c r="F29" s="56"/>
+      <c r="G29" s="57"/>
     </row>
     <row r="30" spans="2:11" ht="18" customHeight="1">
       <c r="B30" s="11" t="s">
@@ -9940,9 +8591,7 @@
       <c r="G30" s="12"/>
     </row>
     <row r="31" spans="2:11" ht="18" customHeight="1">
-      <c r="B31" s="43" t="s">
-        <v>47</v>
-      </c>
+      <c r="B31" s="43"/>
       <c r="C31" s="12"/>
       <c r="D31" s="12"/>
       <c r="E31" s="12"/>
